--- a/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_DSM_Ramping.xlsx
+++ b/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_DSM_Ramping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tom\Tu Graz\Masterarbeit\Git\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6D4836-6046-423A-8DDB-4991D33B805F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3470F267-1037-45EF-B39F-00A79FB1D620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="233">
   <si>
     <t>Power - Bus information</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Zone</t>
   </si>
   <si>
-    <t>Minimum Voltage</t>
-  </si>
-  <si>
     <t>Zone of Interest</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>z</t>
   </si>
   <si>
-    <t>pBusMinV</t>
-  </si>
-  <si>
     <t>zoi</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t>Zone in which node lies</t>
   </si>
   <si>
-    <t>Minimum voltage (in % of base voltage)</t>
-  </si>
-  <si>
     <t>Whether node is relevant for end result (1) or not (0)</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
     <t>[z]</t>
   </si>
   <si>
-    <t>[p.u.]</t>
-  </si>
-  <si>
     <t>[0, 1]</t>
   </si>
   <si>
@@ -812,13 +800,19 @@
     <t>kn006_CO</t>
   </si>
   <si>
-    <t>DSM_Ramping</t>
-  </si>
-  <si>
     <t>[kn]</t>
   </si>
   <si>
-    <t>DSM_activation_time</t>
+    <t>DSM_Ramping_pos</t>
+  </si>
+  <si>
+    <t>DSM_activation_time_pos</t>
+  </si>
+  <si>
+    <t>DSM_Ramping_neg</t>
+  </si>
+  <si>
+    <t>DSM_activation_time_neg</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1398,12 @@
   <cols>
     <col min="1" max="1" width="5.5546875" customWidth="1"/>
     <col min="2" max="2" width="19.77734375" customWidth="1"/>
-    <col min="3" max="12" width="15.77734375" customWidth="1"/>
+    <col min="3" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="15.77734375" customWidth="1"/>
     <col min="13" max="14" width="20.21875" customWidth="1"/>
     <col min="15" max="16" width="15.77734375" customWidth="1"/>
     <col min="17" max="17" width="18.77734375" customWidth="1"/>
@@ -1456,15 +1455,17 @@
         <v>6</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="18"/>
       <c r="I3" s="18"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1474,38 +1475,40 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="E4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -1515,36 +1518,38 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="20"/>
       <c r="I5" s="20"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -1554,36 +1559,38 @@
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="21"/>
+        <v>24</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="I6" s="21"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
@@ -1593,36 +1600,38 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="22"/>
+        <v>228</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>228</v>
+      </c>
       <c r="I7" s="22"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
@@ -1632,20 +1641,20 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="12">
         <v>1</v>
@@ -1656,10 +1665,12 @@
       <c r="F8" s="23">
         <v>10</v>
       </c>
-      <c r="G8" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H8" s="23"/>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="23">
+        <v>10</v>
+      </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
@@ -1678,7 +1689,7 @@
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
@@ -1689,10 +1700,12 @@
       <c r="F9" s="23">
         <v>10</v>
       </c>
-      <c r="G9" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H9" s="23"/>
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="23">
+        <v>10</v>
+      </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
@@ -1705,17 +1718,17 @@
         <v>1</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
@@ -1726,10 +1739,12 @@
       <c r="F10" s="23">
         <v>10</v>
       </c>
-      <c r="G10" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H10" s="23"/>
+      <c r="G10" s="13">
+        <v>1</v>
+      </c>
+      <c r="H10" s="23">
+        <v>10</v>
+      </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
@@ -1742,17 +1757,17 @@
         <v>1</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
@@ -1763,10 +1778,12 @@
       <c r="F11" s="23">
         <v>10</v>
       </c>
-      <c r="G11" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H11" s="23"/>
+      <c r="G11" s="13">
+        <v>2</v>
+      </c>
+      <c r="H11" s="23">
+        <v>10</v>
+      </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
@@ -1779,17 +1796,17 @@
         <v>1</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S11" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -1800,10 +1817,12 @@
       <c r="F12" s="23">
         <v>10</v>
       </c>
-      <c r="G12" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H12" s="23"/>
+      <c r="G12" s="13">
+        <v>3</v>
+      </c>
+      <c r="H12" s="23">
+        <v>10</v>
+      </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
       <c r="K12" s="23"/>
@@ -1816,17 +1835,17 @@
         <v>1</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D13" s="12">
         <v>1</v>
@@ -1837,10 +1856,12 @@
       <c r="F13" s="23">
         <v>10</v>
       </c>
-      <c r="G13" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H13" s="23"/>
+      <c r="G13" s="13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="23">
+        <v>10</v>
+      </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
@@ -1853,17 +1874,17 @@
         <v>1</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -1874,10 +1895,12 @@
       <c r="F14" s="23">
         <v>10</v>
       </c>
-      <c r="G14" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H14" s="23"/>
+      <c r="G14" s="13">
+        <v>2</v>
+      </c>
+      <c r="H14" s="23">
+        <v>10</v>
+      </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
       <c r="K14" s="23"/>
@@ -1890,17 +1913,17 @@
         <v>1</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
@@ -1911,10 +1934,12 @@
       <c r="F15" s="23">
         <v>10</v>
       </c>
-      <c r="G15" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H15" s="23"/>
+      <c r="G15" s="13">
+        <v>3</v>
+      </c>
+      <c r="H15" s="23">
+        <v>10</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -1927,17 +1952,17 @@
         <v>1</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -1948,10 +1973,12 @@
       <c r="F16" s="23">
         <v>10</v>
       </c>
-      <c r="G16" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H16" s="23"/>
+      <c r="G16" s="13">
+        <v>1</v>
+      </c>
+      <c r="H16" s="23">
+        <v>10</v>
+      </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
       <c r="K16" s="23"/>
@@ -1964,17 +1991,17 @@
         <v>1</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D17" s="12">
         <v>1</v>
@@ -1985,10 +2012,12 @@
       <c r="F17" s="23">
         <v>10</v>
       </c>
-      <c r="G17" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H17" s="23"/>
+      <c r="G17" s="13">
+        <v>2</v>
+      </c>
+      <c r="H17" s="23">
+        <v>10</v>
+      </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
       <c r="K17" s="23"/>
@@ -2001,17 +2030,17 @@
         <v>1</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D18" s="12">
         <v>1</v>
@@ -2022,10 +2051,12 @@
       <c r="F18" s="23">
         <v>10</v>
       </c>
-      <c r="G18" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H18" s="23"/>
+      <c r="G18" s="13">
+        <v>3</v>
+      </c>
+      <c r="H18" s="23">
+        <v>10</v>
+      </c>
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
       <c r="K18" s="23"/>
@@ -2038,17 +2069,17 @@
         <v>1</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -2059,10 +2090,12 @@
       <c r="F19" s="23">
         <v>10</v>
       </c>
-      <c r="G19" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H19" s="23"/>
+      <c r="G19" s="13">
+        <v>1</v>
+      </c>
+      <c r="H19" s="23">
+        <v>10</v>
+      </c>
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
       <c r="K19" s="23"/>
@@ -2075,17 +2108,17 @@
         <v>1</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S19" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -2096,10 +2129,12 @@
       <c r="F20" s="23">
         <v>10</v>
       </c>
-      <c r="G20" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H20" s="23"/>
+      <c r="G20" s="13">
+        <v>2</v>
+      </c>
+      <c r="H20" s="23">
+        <v>10</v>
+      </c>
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
       <c r="K20" s="23"/>
@@ -2112,17 +2147,17 @@
         <v>1</v>
       </c>
       <c r="R20" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S20" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -2133,10 +2168,12 @@
       <c r="F21" s="23">
         <v>10</v>
       </c>
-      <c r="G21" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H21" s="23"/>
+      <c r="G21" s="13">
+        <v>3</v>
+      </c>
+      <c r="H21" s="23">
+        <v>10</v>
+      </c>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
@@ -2149,17 +2186,17 @@
         <v>1</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -2170,10 +2207,12 @@
       <c r="F22" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G22" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H22" s="23"/>
+      <c r="G22" s="13">
+        <v>21</v>
+      </c>
+      <c r="H22" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
@@ -2186,17 +2225,17 @@
         <v>1</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -2207,10 +2246,12 @@
       <c r="F23" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G23" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H23" s="23"/>
+      <c r="G23" s="13">
+        <v>21</v>
+      </c>
+      <c r="H23" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
@@ -2223,17 +2264,17 @@
         <v>1</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
@@ -2244,10 +2285,12 @@
       <c r="F24" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G24" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H24" s="23"/>
+      <c r="G24" s="13">
+        <v>21</v>
+      </c>
+      <c r="H24" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
@@ -2260,17 +2303,17 @@
         <v>1</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S24" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D25" s="12">
         <v>1</v>
@@ -2281,10 +2324,12 @@
       <c r="F25" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G25" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H25" s="23"/>
+      <c r="G25" s="13">
+        <v>21</v>
+      </c>
+      <c r="H25" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
@@ -2297,17 +2342,17 @@
         <v>1</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S25" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D26" s="12">
         <v>1</v>
@@ -2318,10 +2363,12 @@
       <c r="F26" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G26" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H26" s="23"/>
+      <c r="G26" s="13">
+        <v>21</v>
+      </c>
+      <c r="H26" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
       <c r="K26" s="23"/>
@@ -2334,17 +2381,17 @@
         <v>1</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S26" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
@@ -2355,10 +2402,12 @@
       <c r="F27" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G27" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H27" s="23"/>
+      <c r="G27" s="13">
+        <v>21</v>
+      </c>
+      <c r="H27" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
       <c r="K27" s="23"/>
@@ -2371,17 +2420,17 @@
         <v>1</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S27" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D28" s="12">
         <v>1</v>
@@ -2392,10 +2441,12 @@
       <c r="F28" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G28" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H28" s="23"/>
+      <c r="G28" s="13">
+        <v>21</v>
+      </c>
+      <c r="H28" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
@@ -2408,17 +2459,17 @@
         <v>1</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S28" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
@@ -2429,10 +2480,12 @@
       <c r="F29" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G29" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H29" s="23"/>
+      <c r="G29" s="13">
+        <v>21</v>
+      </c>
+      <c r="H29" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
@@ -2445,17 +2498,17 @@
         <v>1</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S29" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
@@ -2466,10 +2519,12 @@
       <c r="F30" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G30" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H30" s="23"/>
+      <c r="G30" s="13">
+        <v>21</v>
+      </c>
+      <c r="H30" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
       <c r="K30" s="23"/>
@@ -2482,17 +2537,17 @@
         <v>1</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S30" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -2503,10 +2558,12 @@
       <c r="F31" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G31" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H31" s="23"/>
+      <c r="G31" s="13">
+        <v>21</v>
+      </c>
+      <c r="H31" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
@@ -2519,17 +2576,17 @@
         <v>1</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -2540,10 +2597,12 @@
       <c r="F32" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G32" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H32" s="23"/>
+      <c r="G32" s="13">
+        <v>21</v>
+      </c>
+      <c r="H32" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
       <c r="K32" s="23"/>
@@ -2556,17 +2615,17 @@
         <v>1</v>
       </c>
       <c r="R32" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S32" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -2577,10 +2636,12 @@
       <c r="F33" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G33" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H33" s="23"/>
+      <c r="G33" s="13">
+        <v>21</v>
+      </c>
+      <c r="H33" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
       <c r="K33" s="23"/>
@@ -2593,17 +2654,17 @@
         <v>1</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -2614,10 +2675,12 @@
       <c r="F34" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G34" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H34" s="23"/>
+      <c r="G34" s="13">
+        <v>21</v>
+      </c>
+      <c r="H34" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
       <c r="K34" s="23"/>
@@ -2630,17 +2693,17 @@
         <v>1</v>
       </c>
       <c r="R34" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S34" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -2651,10 +2714,12 @@
       <c r="F35" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G35" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H35" s="23"/>
+      <c r="G35" s="13">
+        <v>21</v>
+      </c>
+      <c r="H35" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
       <c r="K35" s="23"/>
@@ -2667,17 +2732,17 @@
         <v>1</v>
       </c>
       <c r="R35" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S35" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -2688,10 +2753,12 @@
       <c r="F36" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G36" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H36" s="23"/>
+      <c r="G36" s="13">
+        <v>21</v>
+      </c>
+      <c r="H36" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
       <c r="K36" s="23"/>
@@ -2704,17 +2771,17 @@
         <v>1</v>
       </c>
       <c r="R36" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -2725,10 +2792,12 @@
       <c r="F37" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G37" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H37" s="23"/>
+      <c r="G37" s="13">
+        <v>21</v>
+      </c>
+      <c r="H37" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
       <c r="K37" s="23"/>
@@ -2741,17 +2810,17 @@
         <v>1</v>
       </c>
       <c r="R37" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
@@ -2762,10 +2831,12 @@
       <c r="F38" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G38" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H38" s="23"/>
+      <c r="G38" s="13">
+        <v>21</v>
+      </c>
+      <c r="H38" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
       <c r="K38" s="23"/>
@@ -2778,17 +2849,17 @@
         <v>1</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -2799,10 +2870,12 @@
       <c r="F39" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G39" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H39" s="23"/>
+      <c r="G39" s="13">
+        <v>21</v>
+      </c>
+      <c r="H39" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
       <c r="K39" s="23"/>
@@ -2815,17 +2888,17 @@
         <v>1</v>
       </c>
       <c r="R39" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
@@ -2836,10 +2909,12 @@
       <c r="F40" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G40" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H40" s="23"/>
+      <c r="G40" s="13">
+        <v>21</v>
+      </c>
+      <c r="H40" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
       <c r="K40" s="23"/>
@@ -2852,17 +2927,17 @@
         <v>1</v>
       </c>
       <c r="R40" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S40" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -2873,10 +2948,12 @@
       <c r="F41" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G41" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H41" s="23"/>
+      <c r="G41" s="13">
+        <v>21</v>
+      </c>
+      <c r="H41" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
       <c r="K41" s="23"/>
@@ -2889,17 +2966,17 @@
         <v>1</v>
       </c>
       <c r="R41" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S41" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -2910,10 +2987,12 @@
       <c r="F42" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G42" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H42" s="23"/>
+      <c r="G42" s="13">
+        <v>21</v>
+      </c>
+      <c r="H42" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
       <c r="K42" s="23"/>
@@ -2926,17 +3005,17 @@
         <v>1</v>
       </c>
       <c r="R42" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S42" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -2947,10 +3026,12 @@
       <c r="F43" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G43" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H43" s="23"/>
+      <c r="G43" s="13">
+        <v>21</v>
+      </c>
+      <c r="H43" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
       <c r="K43" s="23"/>
@@ -2963,17 +3044,17 @@
         <v>1</v>
       </c>
       <c r="R43" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S43" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -2984,10 +3065,12 @@
       <c r="F44" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G44" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H44" s="23"/>
+      <c r="G44" s="13">
+        <v>21</v>
+      </c>
+      <c r="H44" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
       <c r="K44" s="23"/>
@@ -3000,17 +3083,17 @@
         <v>1</v>
       </c>
       <c r="R44" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S44" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D45" s="12">
         <v>1</v>
@@ -3021,10 +3104,12 @@
       <c r="F45" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G45" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H45" s="23"/>
+      <c r="G45" s="13">
+        <v>21</v>
+      </c>
+      <c r="H45" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
       <c r="K45" s="23"/>
@@ -3037,17 +3122,17 @@
         <v>1</v>
       </c>
       <c r="R45" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S45" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -3058,10 +3143,12 @@
       <c r="F46" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G46" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H46" s="23"/>
+      <c r="G46" s="13">
+        <v>21</v>
+      </c>
+      <c r="H46" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
       <c r="K46" s="23"/>
@@ -3074,17 +3161,17 @@
         <v>1</v>
       </c>
       <c r="R46" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S46" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -3095,10 +3182,12 @@
       <c r="F47" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G47" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H47" s="23"/>
+      <c r="G47" s="13">
+        <v>21</v>
+      </c>
+      <c r="H47" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
       <c r="K47" s="23"/>
@@ -3111,17 +3200,17 @@
         <v>1</v>
       </c>
       <c r="R47" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S47" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D48" s="12">
         <v>1</v>
@@ -3132,10 +3221,12 @@
       <c r="F48" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G48" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H48" s="23"/>
+      <c r="G48" s="13">
+        <v>21</v>
+      </c>
+      <c r="H48" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
       <c r="K48" s="23"/>
@@ -3148,17 +3239,17 @@
         <v>1</v>
       </c>
       <c r="R48" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S48" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -3169,10 +3260,12 @@
       <c r="F49" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G49" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H49" s="23"/>
+      <c r="G49" s="13">
+        <v>21</v>
+      </c>
+      <c r="H49" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
       <c r="K49" s="23"/>
@@ -3185,17 +3278,17 @@
         <v>1</v>
       </c>
       <c r="R49" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S49" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -3206,10 +3299,12 @@
       <c r="F50" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G50" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H50" s="23"/>
+      <c r="G50" s="13">
+        <v>21</v>
+      </c>
+      <c r="H50" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
       <c r="K50" s="23"/>
@@ -3222,17 +3317,17 @@
         <v>1</v>
       </c>
       <c r="R50" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S50" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D51" s="12">
         <v>1</v>
@@ -3243,10 +3338,12 @@
       <c r="F51" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G51" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H51" s="23"/>
+      <c r="G51" s="13">
+        <v>21</v>
+      </c>
+      <c r="H51" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
       <c r="K51" s="23"/>
@@ -3259,17 +3356,17 @@
         <v>1</v>
       </c>
       <c r="R51" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S51" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
@@ -3280,10 +3377,12 @@
       <c r="F52" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G52" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H52" s="23"/>
+      <c r="G52" s="13">
+        <v>21</v>
+      </c>
+      <c r="H52" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
       <c r="K52" s="23"/>
@@ -3296,17 +3395,17 @@
         <v>1</v>
       </c>
       <c r="R52" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S52" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
@@ -3317,10 +3416,12 @@
       <c r="F53" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G53" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H53" s="23"/>
+      <c r="G53" s="13">
+        <v>21</v>
+      </c>
+      <c r="H53" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
       <c r="K53" s="23"/>
@@ -3333,17 +3434,17 @@
         <v>1</v>
       </c>
       <c r="R53" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S53" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="11"/>
       <c r="C54" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D54" s="12">
         <v>1</v>
@@ -3354,10 +3455,12 @@
       <c r="F54" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G54" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H54" s="23"/>
+      <c r="G54" s="13">
+        <v>21</v>
+      </c>
+      <c r="H54" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I54" s="23"/>
       <c r="J54" s="23"/>
       <c r="K54" s="23"/>
@@ -3370,17 +3473,17 @@
         <v>1</v>
       </c>
       <c r="R54" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S54" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="11"/>
       <c r="C55" s="12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -3391,10 +3494,12 @@
       <c r="F55" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G55" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H55" s="23"/>
+      <c r="G55" s="13">
+        <v>21</v>
+      </c>
+      <c r="H55" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I55" s="23"/>
       <c r="J55" s="23"/>
       <c r="K55" s="23"/>
@@ -3407,17 +3512,17 @@
         <v>1</v>
       </c>
       <c r="R55" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S55" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D56" s="12">
         <v>1</v>
@@ -3428,10 +3533,12 @@
       <c r="F56" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G56" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H56" s="23"/>
+      <c r="G56" s="13">
+        <v>21</v>
+      </c>
+      <c r="H56" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I56" s="23"/>
       <c r="J56" s="23"/>
       <c r="K56" s="23"/>
@@ -3444,17 +3551,17 @@
         <v>1</v>
       </c>
       <c r="R56" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S56" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D57" s="12">
         <v>1</v>
@@ -3465,10 +3572,12 @@
       <c r="F57" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G57" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H57" s="23"/>
+      <c r="G57" s="13">
+        <v>21</v>
+      </c>
+      <c r="H57" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I57" s="23"/>
       <c r="J57" s="23"/>
       <c r="K57" s="23"/>
@@ -3481,17 +3590,17 @@
         <v>1</v>
       </c>
       <c r="R57" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S57" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -3502,10 +3611,12 @@
       <c r="F58" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G58" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H58" s="23"/>
+      <c r="G58" s="13">
+        <v>21</v>
+      </c>
+      <c r="H58" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I58" s="23"/>
       <c r="J58" s="23"/>
       <c r="K58" s="23"/>
@@ -3518,17 +3629,17 @@
         <v>1</v>
       </c>
       <c r="R58" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S58" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -3539,10 +3650,12 @@
       <c r="F59" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G59" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H59" s="23"/>
+      <c r="G59" s="13">
+        <v>21</v>
+      </c>
+      <c r="H59" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I59" s="23"/>
       <c r="J59" s="23"/>
       <c r="K59" s="23"/>
@@ -3555,17 +3668,17 @@
         <v>1</v>
       </c>
       <c r="R59" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S59" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
@@ -3576,10 +3689,12 @@
       <c r="F60" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G60" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H60" s="23"/>
+      <c r="G60" s="13">
+        <v>21</v>
+      </c>
+      <c r="H60" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I60" s="23"/>
       <c r="J60" s="23"/>
       <c r="K60" s="23"/>
@@ -3592,17 +3707,17 @@
         <v>1</v>
       </c>
       <c r="R60" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S60" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="11"/>
       <c r="C61" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
@@ -3613,10 +3728,12 @@
       <c r="F61" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G61" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H61" s="23"/>
+      <c r="G61" s="13">
+        <v>21</v>
+      </c>
+      <c r="H61" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I61" s="23"/>
       <c r="J61" s="23"/>
       <c r="K61" s="23"/>
@@ -3629,17 +3746,17 @@
         <v>1</v>
       </c>
       <c r="R61" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S61" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="11"/>
       <c r="C62" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D62" s="12">
         <v>1</v>
@@ -3650,10 +3767,12 @@
       <c r="F62" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G62" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H62" s="23"/>
+      <c r="G62" s="13">
+        <v>21</v>
+      </c>
+      <c r="H62" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
       <c r="K62" s="23"/>
@@ -3666,17 +3785,17 @@
         <v>1</v>
       </c>
       <c r="R62" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S62" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -3687,10 +3806,12 @@
       <c r="F63" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G63" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H63" s="23"/>
+      <c r="G63" s="13">
+        <v>21</v>
+      </c>
+      <c r="H63" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I63" s="23"/>
       <c r="J63" s="23"/>
       <c r="K63" s="23"/>
@@ -3703,17 +3824,17 @@
         <v>1</v>
       </c>
       <c r="R63" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S63" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="11"/>
       <c r="C64" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D64" s="12">
         <v>1</v>
@@ -3724,10 +3845,12 @@
       <c r="F64" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G64" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H64" s="23"/>
+      <c r="G64" s="13">
+        <v>21</v>
+      </c>
+      <c r="H64" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I64" s="23"/>
       <c r="J64" s="23"/>
       <c r="K64" s="23"/>
@@ -3740,17 +3863,17 @@
         <v>1</v>
       </c>
       <c r="R64" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S64" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="11"/>
       <c r="C65" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -3761,10 +3884,12 @@
       <c r="F65" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G65" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H65" s="23"/>
+      <c r="G65" s="13">
+        <v>21</v>
+      </c>
+      <c r="H65" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I65" s="23"/>
       <c r="J65" s="23"/>
       <c r="K65" s="23"/>
@@ -3777,17 +3902,17 @@
         <v>1</v>
       </c>
       <c r="R65" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S65" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
@@ -3798,10 +3923,12 @@
       <c r="F66" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G66" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H66" s="23"/>
+      <c r="G66" s="13">
+        <v>21</v>
+      </c>
+      <c r="H66" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I66" s="23"/>
       <c r="J66" s="23"/>
       <c r="K66" s="23"/>
@@ -3814,17 +3941,17 @@
         <v>1</v>
       </c>
       <c r="R66" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S66" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D67" s="12">
         <v>1</v>
@@ -3835,10 +3962,12 @@
       <c r="F67" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G67" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H67" s="23"/>
+      <c r="G67" s="13">
+        <v>21</v>
+      </c>
+      <c r="H67" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I67" s="23"/>
       <c r="J67" s="23"/>
       <c r="K67" s="23"/>
@@ -3851,17 +3980,17 @@
         <v>1</v>
       </c>
       <c r="R67" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S67" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D68" s="12">
         <v>1</v>
@@ -3872,10 +4001,12 @@
       <c r="F68" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G68" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H68" s="23"/>
+      <c r="G68" s="13">
+        <v>21</v>
+      </c>
+      <c r="H68" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I68" s="23"/>
       <c r="J68" s="23"/>
       <c r="K68" s="23"/>
@@ -3888,17 +4019,17 @@
         <v>1</v>
       </c>
       <c r="R68" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S68" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="11"/>
       <c r="C69" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D69" s="12">
         <v>1</v>
@@ -3909,10 +4040,12 @@
       <c r="F69" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G69" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H69" s="23"/>
+      <c r="G69" s="13">
+        <v>21</v>
+      </c>
+      <c r="H69" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I69" s="23"/>
       <c r="J69" s="23"/>
       <c r="K69" s="23"/>
@@ -3925,17 +4058,17 @@
         <v>1</v>
       </c>
       <c r="R69" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S69" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="11"/>
       <c r="C70" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
@@ -3946,10 +4079,12 @@
       <c r="F70" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G70" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H70" s="23"/>
+      <c r="G70" s="13">
+        <v>21</v>
+      </c>
+      <c r="H70" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I70" s="23"/>
       <c r="J70" s="23"/>
       <c r="K70" s="23"/>
@@ -3962,17 +4097,17 @@
         <v>1</v>
       </c>
       <c r="R70" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S70" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="11"/>
       <c r="C71" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D71" s="12">
         <v>1</v>
@@ -3983,10 +4118,12 @@
       <c r="F71" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G71" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H71" s="23"/>
+      <c r="G71" s="13">
+        <v>21</v>
+      </c>
+      <c r="H71" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I71" s="23"/>
       <c r="J71" s="23"/>
       <c r="K71" s="23"/>
@@ -3999,17 +4136,17 @@
         <v>1</v>
       </c>
       <c r="R71" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S71" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="11"/>
       <c r="C72" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D72" s="12">
         <v>1</v>
@@ -4020,10 +4157,12 @@
       <c r="F72" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G72" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H72" s="23"/>
+      <c r="G72" s="13">
+        <v>21</v>
+      </c>
+      <c r="H72" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I72" s="23"/>
       <c r="J72" s="23"/>
       <c r="K72" s="23"/>
@@ -4036,17 +4175,17 @@
         <v>1</v>
       </c>
       <c r="R72" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S72" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D73" s="12">
         <v>1</v>
@@ -4057,10 +4196,12 @@
       <c r="F73" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G73" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H73" s="23"/>
+      <c r="G73" s="13">
+        <v>21</v>
+      </c>
+      <c r="H73" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I73" s="23"/>
       <c r="J73" s="23"/>
       <c r="K73" s="23"/>
@@ -4073,17 +4214,17 @@
         <v>1</v>
       </c>
       <c r="R73" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S73" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="11"/>
       <c r="C74" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D74" s="12">
         <v>1</v>
@@ -4094,10 +4235,12 @@
       <c r="F74" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G74" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H74" s="23"/>
+      <c r="G74" s="13">
+        <v>21</v>
+      </c>
+      <c r="H74" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I74" s="23"/>
       <c r="J74" s="23"/>
       <c r="K74" s="23"/>
@@ -4110,17 +4253,17 @@
         <v>1</v>
       </c>
       <c r="R74" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S74" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="11"/>
       <c r="C75" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D75" s="12">
         <v>1</v>
@@ -4131,10 +4274,12 @@
       <c r="F75" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G75" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H75" s="23"/>
+      <c r="G75" s="13">
+        <v>21</v>
+      </c>
+      <c r="H75" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I75" s="23"/>
       <c r="J75" s="23"/>
       <c r="K75" s="23"/>
@@ -4147,17 +4292,17 @@
         <v>1</v>
       </c>
       <c r="R75" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S75" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="11"/>
       <c r="C76" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D76" s="12">
         <v>1</v>
@@ -4168,10 +4313,12 @@
       <c r="F76" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G76" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H76" s="23"/>
+      <c r="G76" s="13">
+        <v>21</v>
+      </c>
+      <c r="H76" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I76" s="23"/>
       <c r="J76" s="23"/>
       <c r="K76" s="23"/>
@@ -4184,17 +4331,17 @@
         <v>1</v>
       </c>
       <c r="R76" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S76" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="11"/>
       <c r="C77" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D77" s="12">
         <v>1</v>
@@ -4205,10 +4352,12 @@
       <c r="F77" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G77" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H77" s="23"/>
+      <c r="G77" s="13">
+        <v>21</v>
+      </c>
+      <c r="H77" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I77" s="23"/>
       <c r="J77" s="23"/>
       <c r="K77" s="23"/>
@@ -4221,17 +4370,17 @@
         <v>1</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S77" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="11"/>
       <c r="C78" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D78" s="12">
         <v>1</v>
@@ -4242,10 +4391,12 @@
       <c r="F78" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G78" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H78" s="23"/>
+      <c r="G78" s="13">
+        <v>21</v>
+      </c>
+      <c r="H78" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I78" s="23"/>
       <c r="J78" s="23"/>
       <c r="K78" s="23"/>
@@ -4258,17 +4409,17 @@
         <v>1</v>
       </c>
       <c r="R78" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S78" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="11"/>
       <c r="C79" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D79" s="12">
         <v>1</v>
@@ -4279,10 +4430,12 @@
       <c r="F79" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G79" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H79" s="23"/>
+      <c r="G79" s="13">
+        <v>21</v>
+      </c>
+      <c r="H79" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I79" s="23"/>
       <c r="J79" s="23"/>
       <c r="K79" s="23"/>
@@ -4295,17 +4448,17 @@
         <v>1</v>
       </c>
       <c r="R79" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S79" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="11"/>
       <c r="C80" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D80" s="12">
         <v>1</v>
@@ -4316,10 +4469,12 @@
       <c r="F80" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G80" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H80" s="23"/>
+      <c r="G80" s="13">
+        <v>21</v>
+      </c>
+      <c r="H80" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I80" s="23"/>
       <c r="J80" s="23"/>
       <c r="K80" s="23"/>
@@ -4332,17 +4487,17 @@
         <v>1</v>
       </c>
       <c r="R80" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S80" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="11"/>
       <c r="C81" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D81" s="12">
         <v>1</v>
@@ -4353,10 +4508,12 @@
       <c r="F81" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G81" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H81" s="23"/>
+      <c r="G81" s="13">
+        <v>21</v>
+      </c>
+      <c r="H81" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I81" s="23"/>
       <c r="J81" s="23"/>
       <c r="K81" s="23"/>
@@ -4369,17 +4526,17 @@
         <v>1</v>
       </c>
       <c r="R81" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S81" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="11"/>
       <c r="C82" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D82" s="12">
         <v>1</v>
@@ -4390,10 +4547,12 @@
       <c r="F82" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G82" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H82" s="23"/>
+      <c r="G82" s="13">
+        <v>21</v>
+      </c>
+      <c r="H82" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I82" s="23"/>
       <c r="J82" s="23"/>
       <c r="K82" s="23"/>
@@ -4406,17 +4565,17 @@
         <v>1</v>
       </c>
       <c r="R82" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S82" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="11"/>
       <c r="C83" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D83" s="12">
         <v>1</v>
@@ -4427,10 +4586,12 @@
       <c r="F83" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G83" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H83" s="23"/>
+      <c r="G83" s="13">
+        <v>21</v>
+      </c>
+      <c r="H83" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I83" s="23"/>
       <c r="J83" s="23"/>
       <c r="K83" s="23"/>
@@ -4443,17 +4604,17 @@
         <v>1</v>
       </c>
       <c r="R83" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S83" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="11"/>
       <c r="C84" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D84" s="12">
         <v>1</v>
@@ -4464,10 +4625,12 @@
       <c r="F84" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G84" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H84" s="23"/>
+      <c r="G84" s="13">
+        <v>21</v>
+      </c>
+      <c r="H84" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I84" s="23"/>
       <c r="J84" s="23"/>
       <c r="K84" s="23"/>
@@ -4480,17 +4643,17 @@
         <v>1</v>
       </c>
       <c r="R84" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S84" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="11"/>
       <c r="C85" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D85" s="12">
         <v>1</v>
@@ -4501,10 +4664,12 @@
       <c r="F85" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G85" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H85" s="23"/>
+      <c r="G85" s="13">
+        <v>21</v>
+      </c>
+      <c r="H85" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I85" s="23"/>
       <c r="J85" s="23"/>
       <c r="K85" s="23"/>
@@ -4517,17 +4682,17 @@
         <v>1</v>
       </c>
       <c r="R85" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S85" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D86" s="12">
         <v>1</v>
@@ -4538,10 +4703,12 @@
       <c r="F86" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G86" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H86" s="23"/>
+      <c r="G86" s="13">
+        <v>21</v>
+      </c>
+      <c r="H86" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I86" s="23"/>
       <c r="J86" s="23"/>
       <c r="K86" s="23"/>
@@ -4554,17 +4721,17 @@
         <v>1</v>
       </c>
       <c r="R86" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S86" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="11"/>
       <c r="C87" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D87" s="12">
         <v>1</v>
@@ -4575,10 +4742,12 @@
       <c r="F87" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G87" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H87" s="23"/>
+      <c r="G87" s="13">
+        <v>21</v>
+      </c>
+      <c r="H87" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I87" s="23"/>
       <c r="J87" s="23"/>
       <c r="K87" s="23"/>
@@ -4591,17 +4760,17 @@
         <v>1</v>
       </c>
       <c r="R87" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S87" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="11"/>
       <c r="C88" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D88" s="12">
         <v>1</v>
@@ -4612,10 +4781,12 @@
       <c r="F88" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G88" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H88" s="23"/>
+      <c r="G88" s="13">
+        <v>21</v>
+      </c>
+      <c r="H88" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I88" s="23"/>
       <c r="J88" s="23"/>
       <c r="K88" s="23"/>
@@ -4628,17 +4799,17 @@
         <v>1</v>
       </c>
       <c r="R88" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S88" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="11"/>
       <c r="C89" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D89" s="12">
         <v>1</v>
@@ -4649,10 +4820,12 @@
       <c r="F89" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G89" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H89" s="23"/>
+      <c r="G89" s="13">
+        <v>21</v>
+      </c>
+      <c r="H89" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I89" s="23"/>
       <c r="J89" s="23"/>
       <c r="K89" s="23"/>
@@ -4665,17 +4838,17 @@
         <v>1</v>
       </c>
       <c r="R89" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S89" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="11"/>
       <c r="C90" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D90" s="12">
         <v>1</v>
@@ -4686,10 +4859,12 @@
       <c r="F90" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G90" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H90" s="23"/>
+      <c r="G90" s="13">
+        <v>21</v>
+      </c>
+      <c r="H90" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I90" s="23"/>
       <c r="J90" s="23"/>
       <c r="K90" s="23"/>
@@ -4702,17 +4877,17 @@
         <v>1</v>
       </c>
       <c r="R90" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S90" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="11"/>
       <c r="C91" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D91" s="12">
         <v>1</v>
@@ -4723,10 +4898,12 @@
       <c r="F91" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G91" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H91" s="23"/>
+      <c r="G91" s="13">
+        <v>21</v>
+      </c>
+      <c r="H91" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I91" s="23"/>
       <c r="J91" s="23"/>
       <c r="K91" s="23"/>
@@ -4739,17 +4916,17 @@
         <v>1</v>
       </c>
       <c r="R91" s="17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S91" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="11"/>
       <c r="C92" s="12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D92" s="12">
         <v>1</v>
@@ -4760,10 +4937,12 @@
       <c r="F92" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G92" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H92" s="23"/>
+      <c r="G92" s="13">
+        <v>21</v>
+      </c>
+      <c r="H92" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I92" s="23"/>
       <c r="J92" s="23"/>
       <c r="K92" s="23"/>
@@ -4776,17 +4955,17 @@
         <v>1</v>
       </c>
       <c r="R92" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S92" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="11"/>
       <c r="C93" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D93" s="12">
         <v>1</v>
@@ -4797,10 +4976,12 @@
       <c r="F93" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G93" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H93" s="23"/>
+      <c r="G93" s="13">
+        <v>21</v>
+      </c>
+      <c r="H93" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I93" s="23"/>
       <c r="J93" s="23"/>
       <c r="K93" s="23"/>
@@ -4813,17 +4994,17 @@
         <v>1</v>
       </c>
       <c r="R93" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S93" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D94" s="12">
         <v>1</v>
@@ -4834,10 +5015,12 @@
       <c r="F94" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G94" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H94" s="23"/>
+      <c r="G94" s="13">
+        <v>21</v>
+      </c>
+      <c r="H94" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I94" s="23"/>
       <c r="J94" s="23"/>
       <c r="K94" s="23"/>
@@ -4850,17 +5033,17 @@
         <v>1</v>
       </c>
       <c r="R94" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S94" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="11"/>
       <c r="C95" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D95" s="12">
         <v>1</v>
@@ -4871,10 +5054,12 @@
       <c r="F95" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G95" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H95" s="23"/>
+      <c r="G95" s="13">
+        <v>21</v>
+      </c>
+      <c r="H95" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I95" s="23"/>
       <c r="J95" s="23"/>
       <c r="K95" s="23"/>
@@ -4887,17 +5072,17 @@
         <v>1</v>
       </c>
       <c r="R95" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S95" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="11"/>
       <c r="C96" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D96" s="12">
         <v>1</v>
@@ -4908,10 +5093,12 @@
       <c r="F96" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G96" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H96" s="23"/>
+      <c r="G96" s="13">
+        <v>21</v>
+      </c>
+      <c r="H96" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I96" s="23"/>
       <c r="J96" s="23"/>
       <c r="K96" s="23"/>
@@ -4924,17 +5111,17 @@
         <v>1</v>
       </c>
       <c r="R96" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S96" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="11"/>
       <c r="C97" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D97" s="12">
         <v>1</v>
@@ -4945,10 +5132,12 @@
       <c r="F97" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G97" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H97" s="23"/>
+      <c r="G97" s="13">
+        <v>21</v>
+      </c>
+      <c r="H97" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I97" s="23"/>
       <c r="J97" s="23"/>
       <c r="K97" s="23"/>
@@ -4961,17 +5150,17 @@
         <v>1</v>
       </c>
       <c r="R97" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S97" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="11"/>
       <c r="C98" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D98" s="12">
         <v>1</v>
@@ -4982,10 +5171,12 @@
       <c r="F98" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G98" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H98" s="23"/>
+      <c r="G98" s="13">
+        <v>21</v>
+      </c>
+      <c r="H98" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I98" s="23"/>
       <c r="J98" s="23"/>
       <c r="K98" s="23"/>
@@ -4998,17 +5189,17 @@
         <v>1</v>
       </c>
       <c r="R98" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S98" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="11"/>
       <c r="C99" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D99" s="12">
         <v>1</v>
@@ -5019,10 +5210,12 @@
       <c r="F99" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G99" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H99" s="23"/>
+      <c r="G99" s="13">
+        <v>21</v>
+      </c>
+      <c r="H99" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I99" s="23"/>
       <c r="J99" s="23"/>
       <c r="K99" s="23"/>
@@ -5035,17 +5228,17 @@
         <v>1</v>
       </c>
       <c r="R99" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S99" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="11"/>
       <c r="C100" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D100" s="12">
         <v>1</v>
@@ -5056,10 +5249,12 @@
       <c r="F100" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G100" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H100" s="23"/>
+      <c r="G100" s="13">
+        <v>21</v>
+      </c>
+      <c r="H100" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I100" s="23"/>
       <c r="J100" s="23"/>
       <c r="K100" s="23"/>
@@ -5072,17 +5267,17 @@
         <v>1</v>
       </c>
       <c r="R100" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S100" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="11"/>
       <c r="C101" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D101" s="12">
         <v>1</v>
@@ -5093,10 +5288,12 @@
       <c r="F101" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G101" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H101" s="23"/>
+      <c r="G101" s="13">
+        <v>21</v>
+      </c>
+      <c r="H101" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I101" s="23"/>
       <c r="J101" s="23"/>
       <c r="K101" s="23"/>
@@ -5109,17 +5306,17 @@
         <v>1</v>
       </c>
       <c r="R101" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S101" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="11"/>
       <c r="C102" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D102" s="12">
         <v>1</v>
@@ -5130,10 +5327,12 @@
       <c r="F102" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G102" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H102" s="23"/>
+      <c r="G102" s="13">
+        <v>21</v>
+      </c>
+      <c r="H102" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I102" s="23"/>
       <c r="J102" s="23"/>
       <c r="K102" s="23"/>
@@ -5146,17 +5345,17 @@
         <v>1</v>
       </c>
       <c r="R102" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S102" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="11"/>
       <c r="C103" s="12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D103" s="12">
         <v>1</v>
@@ -5167,10 +5366,12 @@
       <c r="F103" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G103" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H103" s="23"/>
+      <c r="G103" s="13">
+        <v>21</v>
+      </c>
+      <c r="H103" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I103" s="23"/>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
@@ -5183,17 +5384,17 @@
         <v>1</v>
       </c>
       <c r="R103" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S103" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="11"/>
       <c r="C104" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D104" s="12">
         <v>1</v>
@@ -5204,10 +5405,12 @@
       <c r="F104" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G104" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H104" s="23"/>
+      <c r="G104" s="13">
+        <v>21</v>
+      </c>
+      <c r="H104" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I104" s="23"/>
       <c r="J104" s="23"/>
       <c r="K104" s="23"/>
@@ -5220,17 +5423,17 @@
         <v>1</v>
       </c>
       <c r="R104" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S104" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="11"/>
       <c r="C105" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D105" s="12">
         <v>1</v>
@@ -5241,10 +5444,12 @@
       <c r="F105" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G105" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H105" s="23"/>
+      <c r="G105" s="13">
+        <v>21</v>
+      </c>
+      <c r="H105" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I105" s="23"/>
       <c r="J105" s="23"/>
       <c r="K105" s="23"/>
@@ -5257,17 +5462,17 @@
         <v>1</v>
       </c>
       <c r="R105" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S105" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="11"/>
       <c r="C106" s="12" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D106" s="12">
         <v>1</v>
@@ -5278,10 +5483,12 @@
       <c r="F106" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G106" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H106" s="23"/>
+      <c r="G106" s="13">
+        <v>21</v>
+      </c>
+      <c r="H106" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I106" s="23"/>
       <c r="J106" s="23"/>
       <c r="K106" s="23"/>
@@ -5294,17 +5501,17 @@
         <v>1</v>
       </c>
       <c r="R106" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S106" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="11"/>
       <c r="C107" s="12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D107" s="12">
         <v>1</v>
@@ -5315,10 +5522,12 @@
       <c r="F107" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G107" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H107" s="23"/>
+      <c r="G107" s="13">
+        <v>21</v>
+      </c>
+      <c r="H107" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I107" s="23"/>
       <c r="J107" s="23"/>
       <c r="K107" s="23"/>
@@ -5331,17 +5540,17 @@
         <v>1</v>
       </c>
       <c r="R107" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S107" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="11"/>
       <c r="C108" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D108" s="12">
         <v>1</v>
@@ -5352,10 +5561,12 @@
       <c r="F108" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G108" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H108" s="23"/>
+      <c r="G108" s="13">
+        <v>21</v>
+      </c>
+      <c r="H108" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I108" s="23"/>
       <c r="J108" s="23"/>
       <c r="K108" s="23"/>
@@ -5368,17 +5579,17 @@
         <v>1</v>
       </c>
       <c r="R108" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S108" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="11"/>
       <c r="C109" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D109" s="12">
         <v>1</v>
@@ -5389,10 +5600,12 @@
       <c r="F109" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G109" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H109" s="23"/>
+      <c r="G109" s="13">
+        <v>21</v>
+      </c>
+      <c r="H109" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I109" s="23"/>
       <c r="J109" s="23"/>
       <c r="K109" s="23"/>
@@ -5405,17 +5618,17 @@
         <v>1</v>
       </c>
       <c r="R109" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S109" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="11"/>
       <c r="C110" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D110" s="12">
         <v>1</v>
@@ -5426,10 +5639,12 @@
       <c r="F110" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G110" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H110" s="23"/>
+      <c r="G110" s="13">
+        <v>21</v>
+      </c>
+      <c r="H110" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I110" s="23"/>
       <c r="J110" s="23"/>
       <c r="K110" s="23"/>
@@ -5442,17 +5657,17 @@
         <v>1</v>
       </c>
       <c r="R110" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S110" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="11"/>
       <c r="C111" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D111" s="12">
         <v>1</v>
@@ -5463,10 +5678,12 @@
       <c r="F111" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G111" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H111" s="23"/>
+      <c r="G111" s="13">
+        <v>21</v>
+      </c>
+      <c r="H111" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I111" s="23"/>
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
@@ -5479,17 +5696,17 @@
         <v>1</v>
       </c>
       <c r="R111" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S111" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="11"/>
       <c r="C112" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D112" s="12">
         <v>1</v>
@@ -5500,10 +5717,12 @@
       <c r="F112" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G112" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H112" s="23"/>
+      <c r="G112" s="13">
+        <v>21</v>
+      </c>
+      <c r="H112" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I112" s="23"/>
       <c r="J112" s="23"/>
       <c r="K112" s="23"/>
@@ -5516,17 +5735,17 @@
         <v>1</v>
       </c>
       <c r="R112" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S112" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="11"/>
       <c r="C113" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D113" s="12">
         <v>1</v>
@@ -5537,10 +5756,12 @@
       <c r="F113" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G113" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H113" s="23"/>
+      <c r="G113" s="13">
+        <v>21</v>
+      </c>
+      <c r="H113" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I113" s="23"/>
       <c r="J113" s="23"/>
       <c r="K113" s="23"/>
@@ -5553,17 +5774,17 @@
         <v>1</v>
       </c>
       <c r="R113" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S113" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="11"/>
       <c r="C114" s="12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D114" s="12">
         <v>1</v>
@@ -5574,10 +5795,12 @@
       <c r="F114" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G114" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H114" s="23"/>
+      <c r="G114" s="13">
+        <v>21</v>
+      </c>
+      <c r="H114" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I114" s="23"/>
       <c r="J114" s="23"/>
       <c r="K114" s="23"/>
@@ -5590,17 +5813,17 @@
         <v>1</v>
       </c>
       <c r="R114" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S114" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="11"/>
       <c r="C115" s="12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D115" s="12">
         <v>1</v>
@@ -5611,10 +5834,12 @@
       <c r="F115" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G115" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H115" s="23"/>
+      <c r="G115" s="13">
+        <v>21</v>
+      </c>
+      <c r="H115" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I115" s="23"/>
       <c r="J115" s="23"/>
       <c r="K115" s="23"/>
@@ -5627,17 +5852,17 @@
         <v>1</v>
       </c>
       <c r="R115" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S115" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="11"/>
       <c r="C116" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D116" s="12">
         <v>1</v>
@@ -5648,10 +5873,12 @@
       <c r="F116" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G116" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H116" s="23"/>
+      <c r="G116" s="13">
+        <v>21</v>
+      </c>
+      <c r="H116" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I116" s="23"/>
       <c r="J116" s="23"/>
       <c r="K116" s="23"/>
@@ -5664,17 +5891,17 @@
         <v>1</v>
       </c>
       <c r="R116" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S116" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="11"/>
       <c r="C117" s="12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D117" s="12">
         <v>1</v>
@@ -5685,10 +5912,12 @@
       <c r="F117" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G117" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H117" s="23"/>
+      <c r="G117" s="13">
+        <v>21</v>
+      </c>
+      <c r="H117" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I117" s="23"/>
       <c r="J117" s="23"/>
       <c r="K117" s="23"/>
@@ -5701,17 +5930,17 @@
         <v>1</v>
       </c>
       <c r="R117" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S117" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="11"/>
       <c r="C118" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D118" s="12">
         <v>1</v>
@@ -5722,10 +5951,12 @@
       <c r="F118" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G118" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H118" s="23"/>
+      <c r="G118" s="13">
+        <v>21</v>
+      </c>
+      <c r="H118" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I118" s="23"/>
       <c r="J118" s="23"/>
       <c r="K118" s="23"/>
@@ -5738,17 +5969,17 @@
         <v>1</v>
       </c>
       <c r="R118" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S118" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="11"/>
       <c r="C119" s="12" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D119" s="12">
         <v>1</v>
@@ -5759,10 +5990,12 @@
       <c r="F119" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G119" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H119" s="23"/>
+      <c r="G119" s="13">
+        <v>21</v>
+      </c>
+      <c r="H119" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I119" s="23"/>
       <c r="J119" s="23"/>
       <c r="K119" s="23"/>
@@ -5775,17 +6008,17 @@
         <v>1</v>
       </c>
       <c r="R119" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S119" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="11"/>
       <c r="C120" s="12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D120" s="12">
         <v>1</v>
@@ -5796,10 +6029,12 @@
       <c r="F120" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G120" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H120" s="23"/>
+      <c r="G120" s="13">
+        <v>21</v>
+      </c>
+      <c r="H120" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I120" s="23"/>
       <c r="J120" s="23"/>
       <c r="K120" s="23"/>
@@ -5812,17 +6047,17 @@
         <v>1</v>
       </c>
       <c r="R120" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S120" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="11"/>
       <c r="C121" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D121" s="12">
         <v>1</v>
@@ -5833,10 +6068,12 @@
       <c r="F121" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G121" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H121" s="23"/>
+      <c r="G121" s="13">
+        <v>21</v>
+      </c>
+      <c r="H121" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I121" s="23"/>
       <c r="J121" s="23"/>
       <c r="K121" s="23"/>
@@ -5849,17 +6086,17 @@
         <v>1</v>
       </c>
       <c r="R121" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S121" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="11"/>
       <c r="C122" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D122" s="12">
         <v>1</v>
@@ -5870,10 +6107,12 @@
       <c r="F122" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G122" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H122" s="23"/>
+      <c r="G122" s="13">
+        <v>21</v>
+      </c>
+      <c r="H122" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I122" s="23"/>
       <c r="J122" s="23"/>
       <c r="K122" s="23"/>
@@ -5886,17 +6125,17 @@
         <v>1</v>
       </c>
       <c r="R122" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S122" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="11"/>
       <c r="C123" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D123" s="12">
         <v>1</v>
@@ -5907,10 +6146,12 @@
       <c r="F123" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G123" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H123" s="23"/>
+      <c r="G123" s="13">
+        <v>21</v>
+      </c>
+      <c r="H123" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I123" s="23"/>
       <c r="J123" s="23"/>
       <c r="K123" s="23"/>
@@ -5923,17 +6164,17 @@
         <v>1</v>
       </c>
       <c r="R123" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S123" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="11"/>
       <c r="C124" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D124" s="12">
         <v>1</v>
@@ -5944,10 +6185,12 @@
       <c r="F124" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G124" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H124" s="23"/>
+      <c r="G124" s="13">
+        <v>21</v>
+      </c>
+      <c r="H124" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I124" s="23"/>
       <c r="J124" s="23"/>
       <c r="K124" s="23"/>
@@ -5960,17 +6203,17 @@
         <v>1</v>
       </c>
       <c r="R124" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S124" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="11"/>
       <c r="C125" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D125" s="12">
         <v>1</v>
@@ -5981,10 +6224,12 @@
       <c r="F125" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G125" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H125" s="23"/>
+      <c r="G125" s="13">
+        <v>21</v>
+      </c>
+      <c r="H125" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I125" s="23"/>
       <c r="J125" s="23"/>
       <c r="K125" s="23"/>
@@ -5997,17 +6242,17 @@
         <v>1</v>
       </c>
       <c r="R125" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S125" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="11"/>
       <c r="C126" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D126" s="12">
         <v>1</v>
@@ -6018,10 +6263,12 @@
       <c r="F126" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G126" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H126" s="23"/>
+      <c r="G126" s="13">
+        <v>21</v>
+      </c>
+      <c r="H126" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I126" s="23"/>
       <c r="J126" s="23"/>
       <c r="K126" s="23"/>
@@ -6034,17 +6281,17 @@
         <v>1</v>
       </c>
       <c r="R126" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S126" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="11"/>
       <c r="C127" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D127" s="12">
         <v>1</v>
@@ -6055,10 +6302,12 @@
       <c r="F127" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G127" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H127" s="23"/>
+      <c r="G127" s="13">
+        <v>21</v>
+      </c>
+      <c r="H127" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I127" s="23"/>
       <c r="J127" s="23"/>
       <c r="K127" s="23"/>
@@ -6071,17 +6320,17 @@
         <v>1</v>
       </c>
       <c r="R127" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S127" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="11"/>
       <c r="C128" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D128" s="12">
         <v>1</v>
@@ -6092,10 +6341,12 @@
       <c r="F128" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G128" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H128" s="23"/>
+      <c r="G128" s="13">
+        <v>21</v>
+      </c>
+      <c r="H128" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I128" s="23"/>
       <c r="J128" s="23"/>
       <c r="K128" s="23"/>
@@ -6108,17 +6359,17 @@
         <v>1</v>
       </c>
       <c r="R128" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S128" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="11"/>
       <c r="C129" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D129" s="12">
         <v>1</v>
@@ -6129,10 +6380,12 @@
       <c r="F129" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G129" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H129" s="23"/>
+      <c r="G129" s="13">
+        <v>21</v>
+      </c>
+      <c r="H129" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I129" s="23"/>
       <c r="J129" s="23"/>
       <c r="K129" s="23"/>
@@ -6145,17 +6398,17 @@
         <v>1</v>
       </c>
       <c r="R129" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S129" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="11"/>
       <c r="C130" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D130" s="12">
         <v>1</v>
@@ -6166,10 +6419,12 @@
       <c r="F130" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G130" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H130" s="23"/>
+      <c r="G130" s="13">
+        <v>21</v>
+      </c>
+      <c r="H130" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I130" s="23"/>
       <c r="J130" s="23"/>
       <c r="K130" s="23"/>
@@ -6182,17 +6437,17 @@
         <v>1</v>
       </c>
       <c r="R130" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S130" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="11"/>
       <c r="C131" s="12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D131" s="12">
         <v>1</v>
@@ -6203,10 +6458,12 @@
       <c r="F131" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G131" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H131" s="23"/>
+      <c r="G131" s="13">
+        <v>21</v>
+      </c>
+      <c r="H131" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I131" s="23"/>
       <c r="J131" s="23"/>
       <c r="K131" s="23"/>
@@ -6219,17 +6476,17 @@
         <v>1</v>
       </c>
       <c r="R131" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S131" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="11"/>
       <c r="C132" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D132" s="12">
         <v>1</v>
@@ -6240,10 +6497,12 @@
       <c r="F132" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G132" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H132" s="23"/>
+      <c r="G132" s="13">
+        <v>21</v>
+      </c>
+      <c r="H132" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I132" s="23"/>
       <c r="J132" s="23"/>
       <c r="K132" s="23"/>
@@ -6256,17 +6515,17 @@
         <v>1</v>
       </c>
       <c r="R132" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S132" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="11"/>
       <c r="C133" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D133" s="12">
         <v>1</v>
@@ -6277,10 +6536,12 @@
       <c r="F133" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G133" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H133" s="23"/>
+      <c r="G133" s="13">
+        <v>21</v>
+      </c>
+      <c r="H133" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I133" s="23"/>
       <c r="J133" s="23"/>
       <c r="K133" s="23"/>
@@ -6293,17 +6554,17 @@
         <v>1</v>
       </c>
       <c r="R133" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S133" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="11"/>
       <c r="C134" s="12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D134" s="12">
         <v>1</v>
@@ -6314,10 +6575,12 @@
       <c r="F134" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G134" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H134" s="23"/>
+      <c r="G134" s="13">
+        <v>21</v>
+      </c>
+      <c r="H134" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I134" s="23"/>
       <c r="J134" s="23"/>
       <c r="K134" s="23"/>
@@ -6330,17 +6593,17 @@
         <v>1</v>
       </c>
       <c r="R134" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S134" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="11"/>
       <c r="C135" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D135" s="12">
         <v>1</v>
@@ -6351,10 +6614,12 @@
       <c r="F135" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G135" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H135" s="23"/>
+      <c r="G135" s="13">
+        <v>21</v>
+      </c>
+      <c r="H135" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I135" s="23"/>
       <c r="J135" s="23"/>
       <c r="K135" s="23"/>
@@ -6367,17 +6632,17 @@
         <v>1</v>
       </c>
       <c r="R135" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S135" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="11"/>
       <c r="C136" s="12" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D136" s="12">
         <v>1</v>
@@ -6388,10 +6653,12 @@
       <c r="F136" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G136" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H136" s="23"/>
+      <c r="G136" s="13">
+        <v>21</v>
+      </c>
+      <c r="H136" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I136" s="23"/>
       <c r="J136" s="23"/>
       <c r="K136" s="23"/>
@@ -6404,17 +6671,17 @@
         <v>1</v>
       </c>
       <c r="R136" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S136" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="11"/>
       <c r="C137" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D137" s="12">
         <v>1</v>
@@ -6425,10 +6692,12 @@
       <c r="F137" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G137" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H137" s="23"/>
+      <c r="G137" s="13">
+        <v>21</v>
+      </c>
+      <c r="H137" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I137" s="23"/>
       <c r="J137" s="23"/>
       <c r="K137" s="23"/>
@@ -6441,17 +6710,17 @@
         <v>1</v>
       </c>
       <c r="R137" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S137" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="11"/>
       <c r="C138" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D138" s="12">
         <v>1</v>
@@ -6462,10 +6731,12 @@
       <c r="F138" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G138" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H138" s="23"/>
+      <c r="G138" s="13">
+        <v>21</v>
+      </c>
+      <c r="H138" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I138" s="23"/>
       <c r="J138" s="23"/>
       <c r="K138" s="23"/>
@@ -6478,17 +6749,17 @@
         <v>1</v>
       </c>
       <c r="R138" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S138" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="11"/>
       <c r="C139" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D139" s="12">
         <v>1</v>
@@ -6499,10 +6770,12 @@
       <c r="F139" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G139" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H139" s="23"/>
+      <c r="G139" s="13">
+        <v>21</v>
+      </c>
+      <c r="H139" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I139" s="23"/>
       <c r="J139" s="23"/>
       <c r="K139" s="23"/>
@@ -6515,17 +6788,17 @@
         <v>1</v>
       </c>
       <c r="R139" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S139" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="11"/>
       <c r="C140" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D140" s="12">
         <v>1</v>
@@ -6536,10 +6809,12 @@
       <c r="F140" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G140" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H140" s="23"/>
+      <c r="G140" s="13">
+        <v>21</v>
+      </c>
+      <c r="H140" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I140" s="23"/>
       <c r="J140" s="23"/>
       <c r="K140" s="23"/>
@@ -6552,17 +6827,17 @@
         <v>1</v>
       </c>
       <c r="R140" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S140" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="11"/>
       <c r="C141" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D141" s="12">
         <v>1</v>
@@ -6573,10 +6848,12 @@
       <c r="F141" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G141" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H141" s="23"/>
+      <c r="G141" s="13">
+        <v>21</v>
+      </c>
+      <c r="H141" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I141" s="23"/>
       <c r="J141" s="23"/>
       <c r="K141" s="23"/>
@@ -6589,17 +6866,17 @@
         <v>1</v>
       </c>
       <c r="R141" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S141" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="11"/>
       <c r="C142" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D142" s="12">
         <v>1</v>
@@ -6610,10 +6887,12 @@
       <c r="F142" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G142" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H142" s="23"/>
+      <c r="G142" s="13">
+        <v>21</v>
+      </c>
+      <c r="H142" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I142" s="23"/>
       <c r="J142" s="23"/>
       <c r="K142" s="23"/>
@@ -6626,17 +6905,17 @@
         <v>1</v>
       </c>
       <c r="R142" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S142" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="11"/>
       <c r="C143" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D143" s="12">
         <v>1</v>
@@ -6647,10 +6926,12 @@
       <c r="F143" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G143" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H143" s="23"/>
+      <c r="G143" s="13">
+        <v>21</v>
+      </c>
+      <c r="H143" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I143" s="23"/>
       <c r="J143" s="23"/>
       <c r="K143" s="23"/>
@@ -6663,17 +6944,17 @@
         <v>1</v>
       </c>
       <c r="R143" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S143" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="11"/>
       <c r="C144" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D144" s="12">
         <v>1</v>
@@ -6684,10 +6965,12 @@
       <c r="F144" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G144" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H144" s="23"/>
+      <c r="G144" s="13">
+        <v>21</v>
+      </c>
+      <c r="H144" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I144" s="23"/>
       <c r="J144" s="23"/>
       <c r="K144" s="23"/>
@@ -6700,17 +6983,17 @@
         <v>1</v>
       </c>
       <c r="R144" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S144" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="11"/>
       <c r="C145" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D145" s="12">
         <v>1</v>
@@ -6721,10 +7004,12 @@
       <c r="F145" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G145" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H145" s="23"/>
+      <c r="G145" s="13">
+        <v>21</v>
+      </c>
+      <c r="H145" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I145" s="23"/>
       <c r="J145" s="23"/>
       <c r="K145" s="23"/>
@@ -6737,17 +7022,17 @@
         <v>1</v>
       </c>
       <c r="R145" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S145" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="11"/>
       <c r="C146" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D146" s="12">
         <v>1</v>
@@ -6758,10 +7043,12 @@
       <c r="F146" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G146" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H146" s="23"/>
+      <c r="G146" s="13">
+        <v>21</v>
+      </c>
+      <c r="H146" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I146" s="23"/>
       <c r="J146" s="23"/>
       <c r="K146" s="23"/>
@@ -6774,17 +7061,17 @@
         <v>1</v>
       </c>
       <c r="R146" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S146" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="11"/>
       <c r="C147" s="12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D147" s="12">
         <v>1</v>
@@ -6795,10 +7082,12 @@
       <c r="F147" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G147" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H147" s="23"/>
+      <c r="G147" s="13">
+        <v>21</v>
+      </c>
+      <c r="H147" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I147" s="23"/>
       <c r="J147" s="23"/>
       <c r="K147" s="23"/>
@@ -6811,17 +7100,17 @@
         <v>1</v>
       </c>
       <c r="R147" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S147" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="11"/>
       <c r="C148" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D148" s="12">
         <v>1</v>
@@ -6832,10 +7121,12 @@
       <c r="F148" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G148" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H148" s="23"/>
+      <c r="G148" s="13">
+        <v>21</v>
+      </c>
+      <c r="H148" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I148" s="23"/>
       <c r="J148" s="23"/>
       <c r="K148" s="23"/>
@@ -6848,17 +7139,17 @@
         <v>1</v>
       </c>
       <c r="R148" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S148" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="11"/>
       <c r="C149" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D149" s="12">
         <v>1</v>
@@ -6869,10 +7160,12 @@
       <c r="F149" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G149" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H149" s="23"/>
+      <c r="G149" s="13">
+        <v>21</v>
+      </c>
+      <c r="H149" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I149" s="23"/>
       <c r="J149" s="23"/>
       <c r="K149" s="23"/>
@@ -6885,17 +7178,17 @@
         <v>1</v>
       </c>
       <c r="R149" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S149" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="11"/>
       <c r="C150" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D150" s="12">
         <v>1</v>
@@ -6906,10 +7199,12 @@
       <c r="F150" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G150" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H150" s="23"/>
+      <c r="G150" s="13">
+        <v>21</v>
+      </c>
+      <c r="H150" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I150" s="23"/>
       <c r="J150" s="23"/>
       <c r="K150" s="23"/>
@@ -6922,17 +7217,17 @@
         <v>1</v>
       </c>
       <c r="R150" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S150" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="11"/>
       <c r="C151" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D151" s="12">
         <v>1</v>
@@ -6943,10 +7238,12 @@
       <c r="F151" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G151" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H151" s="23"/>
+      <c r="G151" s="13">
+        <v>21</v>
+      </c>
+      <c r="H151" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I151" s="23"/>
       <c r="J151" s="23"/>
       <c r="K151" s="23"/>
@@ -6959,17 +7256,17 @@
         <v>1</v>
       </c>
       <c r="R151" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S151" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="11"/>
       <c r="C152" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D152" s="12">
         <v>1</v>
@@ -6980,10 +7277,12 @@
       <c r="F152" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G152" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H152" s="23"/>
+      <c r="G152" s="13">
+        <v>21</v>
+      </c>
+      <c r="H152" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I152" s="23"/>
       <c r="J152" s="23"/>
       <c r="K152" s="23"/>
@@ -6996,17 +7295,17 @@
         <v>1</v>
       </c>
       <c r="R152" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S152" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="11"/>
       <c r="C153" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D153" s="12">
         <v>1</v>
@@ -7017,10 +7316,12 @@
       <c r="F153" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G153" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H153" s="23"/>
+      <c r="G153" s="13">
+        <v>21</v>
+      </c>
+      <c r="H153" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I153" s="23"/>
       <c r="J153" s="23"/>
       <c r="K153" s="23"/>
@@ -7033,17 +7334,17 @@
         <v>1</v>
       </c>
       <c r="R153" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S153" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="11"/>
       <c r="C154" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D154" s="12">
         <v>1</v>
@@ -7054,10 +7355,12 @@
       <c r="F154" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G154" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H154" s="23"/>
+      <c r="G154" s="13">
+        <v>21</v>
+      </c>
+      <c r="H154" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I154" s="23"/>
       <c r="J154" s="23"/>
       <c r="K154" s="23"/>
@@ -7070,17 +7373,17 @@
         <v>1</v>
       </c>
       <c r="R154" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S154" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="11"/>
       <c r="C155" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D155" s="12">
         <v>1</v>
@@ -7091,10 +7394,12 @@
       <c r="F155" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G155" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H155" s="23"/>
+      <c r="G155" s="13">
+        <v>21</v>
+      </c>
+      <c r="H155" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I155" s="23"/>
       <c r="J155" s="23"/>
       <c r="K155" s="23"/>
@@ -7107,17 +7412,17 @@
         <v>1</v>
       </c>
       <c r="R155" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S155" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="11"/>
       <c r="C156" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D156" s="12">
         <v>1</v>
@@ -7128,10 +7433,12 @@
       <c r="F156" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G156" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H156" s="23"/>
+      <c r="G156" s="13">
+        <v>21</v>
+      </c>
+      <c r="H156" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I156" s="23"/>
       <c r="J156" s="23"/>
       <c r="K156" s="23"/>
@@ -7144,17 +7451,17 @@
         <v>1</v>
       </c>
       <c r="R156" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S156" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="11"/>
       <c r="C157" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D157" s="12">
         <v>1</v>
@@ -7165,10 +7472,12 @@
       <c r="F157" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G157" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H157" s="23"/>
+      <c r="G157" s="13">
+        <v>21</v>
+      </c>
+      <c r="H157" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I157" s="23"/>
       <c r="J157" s="23"/>
       <c r="K157" s="23"/>
@@ -7181,17 +7490,17 @@
         <v>1</v>
       </c>
       <c r="R157" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S157" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="11"/>
       <c r="C158" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D158" s="12">
         <v>1</v>
@@ -7202,10 +7511,12 @@
       <c r="F158" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G158" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H158" s="23"/>
+      <c r="G158" s="13">
+        <v>21</v>
+      </c>
+      <c r="H158" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I158" s="23"/>
       <c r="J158" s="23"/>
       <c r="K158" s="23"/>
@@ -7218,17 +7529,17 @@
         <v>1</v>
       </c>
       <c r="R158" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S158" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="11"/>
       <c r="C159" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D159" s="12">
         <v>1</v>
@@ -7239,10 +7550,12 @@
       <c r="F159" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G159" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H159" s="23"/>
+      <c r="G159" s="13">
+        <v>21</v>
+      </c>
+      <c r="H159" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I159" s="23"/>
       <c r="J159" s="23"/>
       <c r="K159" s="23"/>
@@ -7255,17 +7568,17 @@
         <v>1</v>
       </c>
       <c r="R159" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S159" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="11"/>
       <c r="C160" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D160" s="12">
         <v>1</v>
@@ -7276,10 +7589,12 @@
       <c r="F160" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G160" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H160" s="23"/>
+      <c r="G160" s="13">
+        <v>21</v>
+      </c>
+      <c r="H160" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I160" s="23"/>
       <c r="J160" s="23"/>
       <c r="K160" s="23"/>
@@ -7292,17 +7607,17 @@
         <v>1</v>
       </c>
       <c r="R160" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S160" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="11"/>
       <c r="C161" s="12" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D161" s="12">
         <v>1</v>
@@ -7313,10 +7628,12 @@
       <c r="F161" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G161" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H161" s="23"/>
+      <c r="G161" s="13">
+        <v>21</v>
+      </c>
+      <c r="H161" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I161" s="23"/>
       <c r="J161" s="23"/>
       <c r="K161" s="23"/>
@@ -7329,17 +7646,17 @@
         <v>1</v>
       </c>
       <c r="R161" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S161" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="11"/>
       <c r="C162" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D162" s="12">
         <v>1</v>
@@ -7350,10 +7667,12 @@
       <c r="F162" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G162" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H162" s="23"/>
+      <c r="G162" s="13">
+        <v>21</v>
+      </c>
+      <c r="H162" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I162" s="23"/>
       <c r="J162" s="23"/>
       <c r="K162" s="23"/>
@@ -7366,17 +7685,17 @@
         <v>1</v>
       </c>
       <c r="R162" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S162" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="11"/>
       <c r="C163" s="12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D163" s="12">
         <v>1</v>
@@ -7387,10 +7706,12 @@
       <c r="F163" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G163" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H163" s="23"/>
+      <c r="G163" s="13">
+        <v>21</v>
+      </c>
+      <c r="H163" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I163" s="23"/>
       <c r="J163" s="23"/>
       <c r="K163" s="23"/>
@@ -7403,17 +7724,17 @@
         <v>1</v>
       </c>
       <c r="R163" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S163" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="11"/>
       <c r="C164" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D164" s="12">
         <v>1</v>
@@ -7424,10 +7745,12 @@
       <c r="F164" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G164" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H164" s="23"/>
+      <c r="G164" s="13">
+        <v>21</v>
+      </c>
+      <c r="H164" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I164" s="23"/>
       <c r="J164" s="23"/>
       <c r="K164" s="23"/>
@@ -7440,17 +7763,17 @@
         <v>1</v>
       </c>
       <c r="R164" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S164" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="11"/>
       <c r="C165" s="12" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D165" s="12">
         <v>1</v>
@@ -7461,10 +7784,12 @@
       <c r="F165" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G165" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H165" s="23"/>
+      <c r="G165" s="13">
+        <v>21</v>
+      </c>
+      <c r="H165" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I165" s="23"/>
       <c r="J165" s="23"/>
       <c r="K165" s="23"/>
@@ -7477,17 +7802,17 @@
         <v>1</v>
       </c>
       <c r="R165" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S165" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="11"/>
       <c r="C166" s="12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D166" s="12">
         <v>1</v>
@@ -7498,10 +7823,12 @@
       <c r="F166" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G166" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H166" s="23"/>
+      <c r="G166" s="13">
+        <v>21</v>
+      </c>
+      <c r="H166" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I166" s="23"/>
       <c r="J166" s="23"/>
       <c r="K166" s="23"/>
@@ -7514,17 +7841,17 @@
         <v>1</v>
       </c>
       <c r="R166" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S166" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="11"/>
       <c r="C167" s="12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D167" s="12">
         <v>1</v>
@@ -7535,10 +7862,12 @@
       <c r="F167" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G167" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H167" s="23"/>
+      <c r="G167" s="13">
+        <v>21</v>
+      </c>
+      <c r="H167" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I167" s="23"/>
       <c r="J167" s="23"/>
       <c r="K167" s="23"/>
@@ -7551,17 +7880,17 @@
         <v>1</v>
       </c>
       <c r="R167" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S167" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="11"/>
       <c r="C168" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D168" s="12">
         <v>1</v>
@@ -7572,10 +7901,12 @@
       <c r="F168" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G168" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H168" s="23"/>
+      <c r="G168" s="13">
+        <v>21</v>
+      </c>
+      <c r="H168" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I168" s="23"/>
       <c r="J168" s="23"/>
       <c r="K168" s="23"/>
@@ -7588,17 +7919,17 @@
         <v>1</v>
       </c>
       <c r="R168" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S168" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="11"/>
       <c r="C169" s="12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D169" s="12">
         <v>1</v>
@@ -7609,10 +7940,12 @@
       <c r="F169" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G169" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H169" s="23"/>
+      <c r="G169" s="13">
+        <v>21</v>
+      </c>
+      <c r="H169" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I169" s="23"/>
       <c r="J169" s="23"/>
       <c r="K169" s="23"/>
@@ -7625,17 +7958,17 @@
         <v>1</v>
       </c>
       <c r="R169" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S169" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="11"/>
       <c r="C170" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D170" s="12">
         <v>1</v>
@@ -7646,10 +7979,12 @@
       <c r="F170" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G170" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H170" s="23"/>
+      <c r="G170" s="13">
+        <v>21</v>
+      </c>
+      <c r="H170" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I170" s="23"/>
       <c r="J170" s="23"/>
       <c r="K170" s="23"/>
@@ -7662,17 +7997,17 @@
         <v>1</v>
       </c>
       <c r="R170" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S170" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="11"/>
       <c r="C171" s="12" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D171" s="12">
         <v>1</v>
@@ -7683,10 +8018,12 @@
       <c r="F171" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G171" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H171" s="23"/>
+      <c r="G171" s="13">
+        <v>21</v>
+      </c>
+      <c r="H171" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I171" s="23"/>
       <c r="J171" s="23"/>
       <c r="K171" s="23"/>
@@ -7699,17 +8036,17 @@
         <v>1</v>
       </c>
       <c r="R171" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S171" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="11"/>
       <c r="C172" s="12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D172" s="12">
         <v>1</v>
@@ -7720,10 +8057,12 @@
       <c r="F172" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G172" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H172" s="23"/>
+      <c r="G172" s="13">
+        <v>21</v>
+      </c>
+      <c r="H172" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I172" s="23"/>
       <c r="J172" s="23"/>
       <c r="K172" s="23"/>
@@ -7736,17 +8075,17 @@
         <v>1</v>
       </c>
       <c r="R172" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S172" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="11"/>
       <c r="C173" s="12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D173" s="12">
         <v>1</v>
@@ -7757,10 +8096,12 @@
       <c r="F173" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G173" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H173" s="23"/>
+      <c r="G173" s="13">
+        <v>21</v>
+      </c>
+      <c r="H173" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I173" s="23"/>
       <c r="J173" s="23"/>
       <c r="K173" s="23"/>
@@ -7773,17 +8114,17 @@
         <v>1</v>
       </c>
       <c r="R173" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S173" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="11"/>
       <c r="C174" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D174" s="12">
         <v>1</v>
@@ -7794,10 +8135,12 @@
       <c r="F174" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G174" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H174" s="23"/>
+      <c r="G174" s="13">
+        <v>21</v>
+      </c>
+      <c r="H174" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I174" s="23"/>
       <c r="J174" s="23"/>
       <c r="K174" s="23"/>
@@ -7810,17 +8153,17 @@
         <v>1</v>
       </c>
       <c r="R174" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S174" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="11"/>
       <c r="C175" s="12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D175" s="12">
         <v>1</v>
@@ -7831,10 +8174,12 @@
       <c r="F175" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G175" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H175" s="23"/>
+      <c r="G175" s="13">
+        <v>21</v>
+      </c>
+      <c r="H175" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I175" s="23"/>
       <c r="J175" s="23"/>
       <c r="K175" s="23"/>
@@ -7847,17 +8192,17 @@
         <v>1</v>
       </c>
       <c r="R175" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S175" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="11"/>
       <c r="C176" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D176" s="12">
         <v>1</v>
@@ -7868,10 +8213,12 @@
       <c r="F176" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G176" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H176" s="23"/>
+      <c r="G176" s="13">
+        <v>21</v>
+      </c>
+      <c r="H176" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I176" s="23"/>
       <c r="J176" s="23"/>
       <c r="K176" s="23"/>
@@ -7884,17 +8231,17 @@
         <v>1</v>
       </c>
       <c r="R176" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S176" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="11"/>
       <c r="C177" s="12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D177" s="12">
         <v>1</v>
@@ -7905,10 +8252,12 @@
       <c r="F177" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G177" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H177" s="23"/>
+      <c r="G177" s="13">
+        <v>21</v>
+      </c>
+      <c r="H177" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I177" s="23"/>
       <c r="J177" s="23"/>
       <c r="K177" s="23"/>
@@ -7921,17 +8270,17 @@
         <v>1</v>
       </c>
       <c r="R177" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S177" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="11"/>
       <c r="C178" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D178" s="12">
         <v>1</v>
@@ -7942,10 +8291,12 @@
       <c r="F178" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G178" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H178" s="23"/>
+      <c r="G178" s="13">
+        <v>21</v>
+      </c>
+      <c r="H178" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I178" s="23"/>
       <c r="J178" s="23"/>
       <c r="K178" s="23"/>
@@ -7958,17 +8309,17 @@
         <v>1</v>
       </c>
       <c r="R178" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S178" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179" s="10"/>
       <c r="B179" s="11"/>
       <c r="C179" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D179" s="12">
         <v>1</v>
@@ -7979,10 +8330,12 @@
       <c r="F179" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G179" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H179" s="23"/>
+      <c r="G179" s="13">
+        <v>21</v>
+      </c>
+      <c r="H179" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I179" s="23"/>
       <c r="J179" s="23"/>
       <c r="K179" s="23"/>
@@ -7995,17 +8348,17 @@
         <v>1</v>
       </c>
       <c r="R179" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S179" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180" s="10"/>
       <c r="B180" s="11"/>
       <c r="C180" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D180" s="12">
         <v>1</v>
@@ -8016,10 +8369,12 @@
       <c r="F180" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G180" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H180" s="23"/>
+      <c r="G180" s="13">
+        <v>21</v>
+      </c>
+      <c r="H180" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I180" s="23"/>
       <c r="J180" s="23"/>
       <c r="K180" s="23"/>
@@ -8032,17 +8387,17 @@
         <v>1</v>
       </c>
       <c r="R180" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S180" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181" s="10"/>
       <c r="B181" s="11"/>
       <c r="C181" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D181" s="12">
         <v>1</v>
@@ -8053,10 +8408,12 @@
       <c r="F181" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G181" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H181" s="23"/>
+      <c r="G181" s="13">
+        <v>21</v>
+      </c>
+      <c r="H181" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I181" s="23"/>
       <c r="J181" s="23"/>
       <c r="K181" s="23"/>
@@ -8069,17 +8426,17 @@
         <v>1</v>
       </c>
       <c r="R181" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S181" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" s="10"/>
       <c r="B182" s="11"/>
       <c r="C182" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D182" s="12">
         <v>1</v>
@@ -8090,10 +8447,12 @@
       <c r="F182" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G182" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H182" s="23"/>
+      <c r="G182" s="13">
+        <v>21</v>
+      </c>
+      <c r="H182" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I182" s="23"/>
       <c r="J182" s="23"/>
       <c r="K182" s="23"/>
@@ -8106,17 +8465,17 @@
         <v>1</v>
       </c>
       <c r="R182" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S182" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" s="10"/>
       <c r="B183" s="11"/>
       <c r="C183" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D183" s="12">
         <v>1</v>
@@ -8127,10 +8486,12 @@
       <c r="F183" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G183" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H183" s="23"/>
+      <c r="G183" s="13">
+        <v>21</v>
+      </c>
+      <c r="H183" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I183" s="23"/>
       <c r="J183" s="23"/>
       <c r="K183" s="23"/>
@@ -8143,17 +8504,17 @@
         <v>1</v>
       </c>
       <c r="R183" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S183" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
       <c r="B184" s="11"/>
       <c r="C184" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D184" s="12">
         <v>1</v>
@@ -8164,10 +8525,12 @@
       <c r="F184" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G184" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H184" s="23"/>
+      <c r="G184" s="13">
+        <v>21</v>
+      </c>
+      <c r="H184" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I184" s="23"/>
       <c r="J184" s="23"/>
       <c r="K184" s="23"/>
@@ -8180,17 +8543,17 @@
         <v>1</v>
       </c>
       <c r="R184" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S184" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" s="10"/>
       <c r="B185" s="11"/>
       <c r="C185" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D185" s="12">
         <v>1</v>
@@ -8201,10 +8564,12 @@
       <c r="F185" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G185" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H185" s="23"/>
+      <c r="G185" s="13">
+        <v>21</v>
+      </c>
+      <c r="H185" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I185" s="23"/>
       <c r="J185" s="23"/>
       <c r="K185" s="23"/>
@@ -8217,17 +8582,17 @@
         <v>1</v>
       </c>
       <c r="R185" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S185" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" s="10"/>
       <c r="B186" s="11"/>
       <c r="C186" s="12" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D186" s="12">
         <v>1</v>
@@ -8238,10 +8603,12 @@
       <c r="F186" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G186" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H186" s="23"/>
+      <c r="G186" s="13">
+        <v>21</v>
+      </c>
+      <c r="H186" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I186" s="23"/>
       <c r="J186" s="23"/>
       <c r="K186" s="23"/>
@@ -8254,17 +8621,17 @@
         <v>1</v>
       </c>
       <c r="R186" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S186" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187" s="10"/>
       <c r="B187" s="11"/>
       <c r="C187" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D187" s="12">
         <v>1</v>
@@ -8275,10 +8642,12 @@
       <c r="F187" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G187" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H187" s="23"/>
+      <c r="G187" s="13">
+        <v>21</v>
+      </c>
+      <c r="H187" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I187" s="23"/>
       <c r="J187" s="23"/>
       <c r="K187" s="23"/>
@@ -8291,17 +8660,17 @@
         <v>1</v>
       </c>
       <c r="R187" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S187" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188" s="10"/>
       <c r="B188" s="11"/>
       <c r="C188" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D188" s="12">
         <v>1</v>
@@ -8312,10 +8681,12 @@
       <c r="F188" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G188" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H188" s="23"/>
+      <c r="G188" s="13">
+        <v>21</v>
+      </c>
+      <c r="H188" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I188" s="23"/>
       <c r="J188" s="23"/>
       <c r="K188" s="23"/>
@@ -8328,17 +8699,17 @@
         <v>1</v>
       </c>
       <c r="R188" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S188" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189" s="10"/>
       <c r="B189" s="11"/>
       <c r="C189" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D189" s="12">
         <v>1</v>
@@ -8349,10 +8720,12 @@
       <c r="F189" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G189" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H189" s="23"/>
+      <c r="G189" s="13">
+        <v>21</v>
+      </c>
+      <c r="H189" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I189" s="23"/>
       <c r="J189" s="23"/>
       <c r="K189" s="23"/>
@@ -8365,17 +8738,17 @@
         <v>1</v>
       </c>
       <c r="R189" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S189" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190" s="10"/>
       <c r="B190" s="11"/>
       <c r="C190" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D190" s="12">
         <v>1</v>
@@ -8386,10 +8759,12 @@
       <c r="F190" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G190" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H190" s="23"/>
+      <c r="G190" s="13">
+        <v>21</v>
+      </c>
+      <c r="H190" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I190" s="23"/>
       <c r="J190" s="23"/>
       <c r="K190" s="23"/>
@@ -8402,17 +8777,17 @@
         <v>1</v>
       </c>
       <c r="R190" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S190" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191" s="10"/>
       <c r="B191" s="11"/>
       <c r="C191" s="12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D191" s="12">
         <v>1</v>
@@ -8423,10 +8798,12 @@
       <c r="F191" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G191" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H191" s="23"/>
+      <c r="G191" s="13">
+        <v>21</v>
+      </c>
+      <c r="H191" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23"/>
       <c r="K191" s="23"/>
@@ -8439,17 +8816,17 @@
         <v>1</v>
       </c>
       <c r="R191" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S191" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192" s="10"/>
       <c r="B192" s="11"/>
       <c r="C192" s="12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D192" s="12">
         <v>1</v>
@@ -8460,10 +8837,12 @@
       <c r="F192" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G192" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H192" s="23"/>
+      <c r="G192" s="13">
+        <v>21</v>
+      </c>
+      <c r="H192" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I192" s="23"/>
       <c r="J192" s="23"/>
       <c r="K192" s="23"/>
@@ -8476,17 +8855,17 @@
         <v>1</v>
       </c>
       <c r="R192" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S192" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A193" s="10"/>
       <c r="B193" s="11"/>
       <c r="C193" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D193" s="12">
         <v>1</v>
@@ -8497,10 +8876,12 @@
       <c r="F193" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G193" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H193" s="23"/>
+      <c r="G193" s="13">
+        <v>21</v>
+      </c>
+      <c r="H193" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I193" s="23"/>
       <c r="J193" s="23"/>
       <c r="K193" s="23"/>
@@ -8513,17 +8894,17 @@
         <v>1</v>
       </c>
       <c r="R193" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S193" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A194" s="10"/>
       <c r="B194" s="11"/>
       <c r="C194" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D194" s="12">
         <v>1</v>
@@ -8534,10 +8915,12 @@
       <c r="F194" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G194" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H194" s="23"/>
+      <c r="G194" s="13">
+        <v>21</v>
+      </c>
+      <c r="H194" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I194" s="23"/>
       <c r="J194" s="23"/>
       <c r="K194" s="23"/>
@@ -8550,17 +8933,17 @@
         <v>1</v>
       </c>
       <c r="R194" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S194" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A195" s="10"/>
       <c r="B195" s="11"/>
       <c r="C195" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D195" s="12">
         <v>1</v>
@@ -8571,10 +8954,12 @@
       <c r="F195" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G195" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H195" s="23"/>
+      <c r="G195" s="13">
+        <v>21</v>
+      </c>
+      <c r="H195" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I195" s="23"/>
       <c r="J195" s="23"/>
       <c r="K195" s="23"/>
@@ -8587,17 +8972,17 @@
         <v>1</v>
       </c>
       <c r="R195" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S195" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A196" s="10"/>
       <c r="B196" s="11"/>
       <c r="C196" s="12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D196" s="12">
         <v>1</v>
@@ -8608,10 +8993,12 @@
       <c r="F196" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G196" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H196" s="23"/>
+      <c r="G196" s="13">
+        <v>21</v>
+      </c>
+      <c r="H196" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I196" s="23"/>
       <c r="J196" s="23"/>
       <c r="K196" s="23"/>
@@ -8624,17 +9011,17 @@
         <v>1</v>
       </c>
       <c r="R196" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S196" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A197" s="10"/>
       <c r="B197" s="11"/>
       <c r="C197" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D197" s="12">
         <v>1</v>
@@ -8645,10 +9032,12 @@
       <c r="F197" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G197" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H197" s="23"/>
+      <c r="G197" s="13">
+        <v>21</v>
+      </c>
+      <c r="H197" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I197" s="23"/>
       <c r="J197" s="23"/>
       <c r="K197" s="23"/>
@@ -8661,17 +9050,17 @@
         <v>1</v>
       </c>
       <c r="R197" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S197" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A198" s="10"/>
       <c r="B198" s="11"/>
       <c r="C198" s="12" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D198" s="12">
         <v>1</v>
@@ -8682,10 +9071,12 @@
       <c r="F198" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G198" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H198" s="23"/>
+      <c r="G198" s="13">
+        <v>21</v>
+      </c>
+      <c r="H198" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I198" s="23"/>
       <c r="J198" s="23"/>
       <c r="K198" s="23"/>
@@ -8698,17 +9089,17 @@
         <v>1</v>
       </c>
       <c r="R198" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S198" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A199" s="10"/>
       <c r="B199" s="11"/>
       <c r="C199" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D199" s="12">
         <v>1</v>
@@ -8719,10 +9110,12 @@
       <c r="F199" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G199" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H199" s="23"/>
+      <c r="G199" s="13">
+        <v>21</v>
+      </c>
+      <c r="H199" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I199" s="23"/>
       <c r="J199" s="23"/>
       <c r="K199" s="23"/>
@@ -8735,17 +9128,17 @@
         <v>1</v>
       </c>
       <c r="R199" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S199" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A200" s="10"/>
       <c r="B200" s="11"/>
       <c r="C200" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D200" s="12">
         <v>1</v>
@@ -8756,10 +9149,12 @@
       <c r="F200" s="23">
         <v>1.0349999999999999</v>
       </c>
-      <c r="G200" s="23">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="H200" s="23"/>
+      <c r="G200" s="13">
+        <v>21</v>
+      </c>
+      <c r="H200" s="23">
+        <v>1.0349999999999999</v>
+      </c>
       <c r="I200" s="23"/>
       <c r="J200" s="23"/>
       <c r="K200" s="23"/>
@@ -8772,10 +9167,10 @@
         <v>2</v>
       </c>
       <c r="R200" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="S200" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_DSM_Ramping.xlsx
+++ b/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_DSM_Ramping.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tom\Tu Graz\Masterarbeit\Git\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3470F267-1037-45EF-B39F-00A79FB1D620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31ED4DE4-7360-48B5-9B52-DA66E247CCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1737,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G10" s="13">
         <v>1</v>
@@ -1776,7 +1789,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G11" s="13">
         <v>2</v>
